--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY266"/>
+  <dimension ref="A1:AZ266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116932555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116933027</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85166132</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85166254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1303,6 +1328,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85166204</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1404,6 +1434,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018303</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1523,6 +1558,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80783821</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1651,6 +1691,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118795581</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1763,6 +1808,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116933082</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1864,6 +1914,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69018304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1977,6 +2032,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92286721</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2092,6 +2152,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122625378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2213,6 +2278,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26168457</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2325,6 +2395,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69762401</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2443,6 +2518,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68731031</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2551,6 +2631,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60899215</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2667,6 +2752,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21260580</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2779,6 +2869,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130608796</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2899,6 +2994,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108820873</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3015,6 +3115,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/45118864</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3153,6 +3258,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116974377</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3272,6 +3382,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84177688</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3388,6 +3503,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/47898217</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3509,6 +3629,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21268402</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3620,6 +3745,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/51579331</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3736,6 +3866,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21260577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3852,6 +3987,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/22114881</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3973,6 +4113,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21274121</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4089,6 +4234,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21254091</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4198,6 +4348,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89261266</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4329,6 +4484,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/24045436</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4465,6 +4625,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101840878</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4581,6 +4746,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21252859</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4702,6 +4872,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26703945</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4818,6 +4993,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26170853</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4938,6 +5118,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132551345</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5054,6 +5239,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26543581</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5170,6 +5360,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/35175502</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5285,6 +5480,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110569914</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5396,6 +5596,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/19803461</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5512,6 +5717,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26156150</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5628,6 +5838,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21244497</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5749,6 +5964,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26156151</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5865,6 +6085,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/36161480</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5984,6 +6209,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109752545</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6100,6 +6330,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21254365</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6216,6 +6451,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/36125839</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6323,6 +6563,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/19204846</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6449,6 +6694,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/19717881</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6565,6 +6815,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21254090</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6681,6 +6936,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21255796</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6800,6 +7060,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773849</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6916,6 +7181,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/42211167</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7023,6 +7293,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/19810975</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7139,6 +7414,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/21257735</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7260,6 +7540,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/26541517</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7381,6 +7666,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/39449038</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7497,6 +7787,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/19268244</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7616,6 +7911,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91806727</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7735,6 +8035,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81853154</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7845,6 +8150,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104433781</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7954,6 +8264,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55649455</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8073,6 +8388,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59074889</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8192,6 +8512,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115474351</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8324,6 +8649,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76895036</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8447,6 +8777,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115452444</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8566,6 +8901,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124394586</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8684,6 +9024,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64841336</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8803,6 +9148,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115897317</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8926,6 +9276,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122610606</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9045,6 +9400,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115692090</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9164,6 +9524,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116420021</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9287,6 +9652,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473842</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9406,6 +9776,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115314708</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9525,6 +9900,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115314762</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9634,6 +10014,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115757554</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9753,6 +10138,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115999433</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9868,6 +10258,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85044789</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9981,6 +10376,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17065879</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10089,6 +10489,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92286944</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10212,6 +10617,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108470002</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10340,6 +10750,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117307594</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10458,6 +10873,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105586523</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10577,6 +10997,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69040821</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10685,6 +11110,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92286960</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10804,6 +11234,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116453883</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10906,6 +11341,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55051</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11022,6 +11462,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2705241</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11135,6 +11580,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56215967</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11248,6 +11698,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56215313</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11360,6 +11815,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130739285</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11484,6 +11944,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101840808</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11607,6 +12072,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61349676</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11706,6 +12176,11 @@
       <c r="AY95" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107438775</t>
         </is>
       </c>
     </row>
@@ -11809,6 +12284,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121561315</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11908,6 +12388,11 @@
       <c r="AY97" t="inlineStr">
         <is>
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107438773</t>
         </is>
       </c>
     </row>
@@ -12011,6 +12496,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104597086</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12112,6 +12602,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107438774</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12224,6 +12719,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130738914</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12343,6 +12843,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61349580</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12453,6 +12958,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118579049</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12572,6 +13082,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106097813</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12679,6 +13194,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5987577</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12791,6 +13311,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5987593</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12904,6 +13429,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71443197</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13019,6 +13549,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104531689</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13130,6 +13665,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2991923</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13242,6 +13782,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5987595</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13351,6 +13896,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61689227</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13460,6 +14010,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61689232</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13575,6 +14130,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120923067</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13676,6 +14236,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104531648</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13796,6 +14361,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61349428</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13917,6 +14487,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2459383</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14030,6 +14605,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15891658</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14146,6 +14726,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3420981</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14248,6 +14833,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104531613</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14351,6 +14941,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5900605</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14463,6 +15058,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5904582</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14575,6 +15175,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5904583</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14687,6 +15292,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5904587</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14794,6 +15404,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5987580</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14892,6 +15507,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6222194</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15000,6 +15620,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6223067</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15109,6 +15734,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71420323</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15221,6 +15851,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6229814</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15319,6 +15954,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6230751</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15428,6 +16068,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71420321</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15547,6 +16192,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134364699</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15657,6 +16307,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495206</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15758,6 +16413,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507724</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15864,6 +16524,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507788</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15965,6 +16630,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104596909</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16066,6 +16736,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019539</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16172,6 +16847,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785863</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16278,6 +16958,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785907</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16384,6 +17069,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785938</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16490,6 +17180,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785952</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16596,6 +17291,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129772308</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16698,6 +17398,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76999152</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16799,6 +17504,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104596921</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16909,6 +17619,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119231337</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17016,6 +17731,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16081878</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17129,6 +17849,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59074063</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17231,6 +17956,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76999128</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17344,6 +18074,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66814419</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17463,6 +18198,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115387338</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17576,6 +18316,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15911919</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17689,6 +18434,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7195576</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17808,6 +18558,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111818804</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17909,6 +18664,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104494953</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18010,6 +18770,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104495089</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18116,6 +18881,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019519</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18222,6 +18992,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104497700</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18328,6 +19103,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019472</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18434,6 +19214,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507670</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18535,6 +19320,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507731</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18642,6 +19432,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742327</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18748,6 +19543,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785843</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18853,6 +19653,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67085823</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18981,6 +19786,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120526593</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19083,6 +19893,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104531310</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19185,6 +20000,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507698</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19287,6 +20107,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104507713</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19405,6 +20230,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/250847</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19522,6 +20352,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61377779</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19649,6 +20484,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/370108</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19767,6 +20607,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1105157</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19888,6 +20733,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14492990</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20005,6 +20855,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14130762</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20129,6 +20984,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117217186</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20241,6 +21101,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2435961</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20354,6 +21219,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7195573</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20467,6 +21337,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71420357</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20580,6 +21455,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71420365</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20699,6 +21579,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115387284</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20818,6 +21703,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116422538</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20935,6 +21825,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66814276</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21054,6 +21949,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88473050</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21173,6 +22073,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87378409</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21281,6 +22186,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6220992</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21388,6 +22298,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6209265</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21505,6 +22420,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65850341</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21602,6 +22522,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154573</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21699,6 +22624,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154574</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21796,6 +22726,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154575</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21893,6 +22828,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154576</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21990,6 +22930,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154578</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22096,6 +23041,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2463604</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22193,6 +23143,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154577</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22300,6 +23255,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5987579</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22406,6 +23366,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129772297</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22507,6 +23472,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785993</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22613,6 +23583,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105342784</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22719,6 +23694,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104494512</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22825,6 +23805,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104494687</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22926,6 +23911,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019453</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -23027,6 +24017,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019735</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23128,6 +24123,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019739</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23229,6 +24229,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019767</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23335,6 +24340,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785798</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23432,6 +24442,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1444159</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23529,6 +24544,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1351375</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23626,6 +24646,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1339045</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23727,6 +24752,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104494832</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23828,6 +24858,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785778</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23946,6 +24981,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54917729</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24069,6 +25109,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55904725</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24184,6 +25229,11 @@
           <t>Dagfjärilar i Södermanland</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14178919</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24299,6 +25349,11 @@
           <t>Dagfjärilar i Södermanland</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14178920</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24414,6 +25469,11 @@
           <t>Dagfjärilar i Södermanland</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14176131</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24542,6 +25602,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86387466</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24655,6 +25720,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55904693</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24761,6 +25831,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416552</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24867,6 +25942,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416553</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24973,6 +26053,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416554</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25079,6 +26164,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104596865</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25192,6 +26282,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6223706</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25300,6 +26395,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6230772</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25401,6 +26501,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785609</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25502,6 +26607,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129785699</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25608,6 +26718,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104494473</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25709,6 +26824,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113019813</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25827,6 +26947,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54917740</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25944,6 +27069,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131228625</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26060,6 +27190,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13088534</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26171,6 +27306,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135100717</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26282,6 +27422,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13088533</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26402,6 +27547,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16081212</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26521,6 +27671,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77001461</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26636,6 +27791,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16081214</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26742,6 +27902,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416549</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26848,6 +28013,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416550</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26954,6 +28124,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416551</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27060,6 +28235,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416561</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27166,6 +28346,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416564</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27289,6 +28474,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110018</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27396,6 +28586,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135100690</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27505,6 +28700,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72566101</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27602,6 +28802,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123154565</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27702,6 +28907,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64954637</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27807,6 +29017,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129772291</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27908,6 +29123,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126705817</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28014,6 +29234,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416555</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28120,6 +29345,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416556</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28226,6 +29456,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416559</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28337,6 +29572,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66729068</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28439,6 +29679,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416176</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28541,6 +29786,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66728625</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28643,6 +29893,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66728626</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28745,6 +30000,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66333157</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28847,6 +30107,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54003</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28958,6 +30223,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78578090</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29060,6 +30330,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54001</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29162,6 +30437,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54002</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29286,6 +30566,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79688746</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29392,6 +30677,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66333240</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29498,6 +30788,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416548</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29604,6 +30899,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416557</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29710,6 +31010,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416558</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29816,6 +31121,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416560</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29922,6 +31232,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66416563</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -30045,6 +31360,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117799414</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30160,6 +31480,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79687073</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30262,8 +31587,280 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66686508</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -27201,7 +27201,7 @@
         <v>135100717</v>
       </c>
       <c r="B228" t="n">
-        <v>43383</v>
+        <v>43388</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>135100690</v>
       </c>
       <c r="B239" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>

--- a/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
+++ b/artfynd/Skäggsmoskogens naturreservat artfynd.xlsx
@@ -28485,7 +28485,7 @@
         <v>135100690</v>
       </c>
       <c r="B239" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
